--- a/diseases/d192/2015-2019.xlsx
+++ b/diseases/d192/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
